--- a/docs/procurement_study/stool-TSG-cloud.xlsx
+++ b/docs/procurement_study/stool-TSG-cloud.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>query "hocker metall schwarz" · 2026-07-15 22:21 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
+          <t>query "barhocker metall metall schwarz" · 2026-07-15 23:21 UTC · destination Bildungscampus, 74076 Heilbronn (DE)</t>
         </is>
       </c>
     </row>
@@ -536,20 +536,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MARIUS Hocker</t>
+          <t>STIG Barhocker</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8516</v>
+        <v>0.9228</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
         <v>5.99</v>
@@ -560,14 +560,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11.99</v>
+        <v>21.99</v>
       </c>
       <c r="K5" t="n">
-        <v>11.99</v>
+        <v>21.99</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/marius-hocker-schwarz-10135659/</t>
+          <t>https://www.ikea.com/de/de/p/stig-barhocker-arbeitsplattenhoehe-schwarz-schwarz-30498418/</t>
         </is>
       </c>
     </row>
@@ -584,20 +584,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARIUS Hocker</t>
+          <t>STIG Barhocker</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8516</v>
+        <v>0.9228</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
         <v>23.96</v>
@@ -608,14 +608,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>83.95999999999999</v>
+        <v>183.96</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/marius-hocker-schwarz-10135659/</t>
+          <t>https://www.ikea.com/de/de/p/stig-barhocker-arbeitsplattenhoehe-schwarz-schwarz-30498418/</t>
         </is>
       </c>
     </row>
@@ -651,28 +651,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STIG Barhocker</t>
+          <t>clp barhocker peony aus pulverbeschichtetem metall minimalistischer look S07F90A9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9228</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.1</v>
+        <v>0.901</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>32.9</v>
       </c>
       <c r="H8" t="n">
-        <v>5.99</v>
+        <v>5.95</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -680,14 +682,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21.99</v>
+        <v>38.85</v>
       </c>
       <c r="K8" t="n">
-        <v>21.99</v>
+        <v>38.85</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/stig-barhocker-arbeitsplattenhoehe-schwarz-schwarz-30498418/</t>
+          <t>https://www.otto.de/p/clp-barhocker-peony-aus-pulverbeschichtetem-metall-minimalistischer-look-S07F90A9/</t>
         </is>
       </c>
     </row>
@@ -699,28 +701,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>STIG Barhocker</t>
+          <t>clp barhocker peony aus pulverbeschichtetem metall minimalistischer look S07F90A9</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9228</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.1</v>
+        <v>0.901</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>32.9</v>
       </c>
       <c r="H9" t="n">
-        <v>23.96</v>
+        <v>23.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -728,40 +732,64 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>183.96</v>
+        <v>352.8</v>
       </c>
       <c r="K9" t="n">
-        <v>18.4</v>
+        <v>35.28</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/stig-barhocker-arbeitsplattenhoehe-schwarz-schwarz-30498418/</t>
+          <t>https://www.otto.de/p/clp-barhocker-peony-aus-pulverbeschichtetem-metall-minimalistischer-look-S07F90A9/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IKEA Deutschland</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>YNGVAR Barhocker</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>179</v>
+      </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>5.99</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90 km round trip @ 0.30 €/km, one trip/order</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>parcel estimate (3/package)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>184.99</v>
+      </c>
+      <c r="K10" t="n">
+        <v>184.99</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.ikea.com/de/de/p/yngvar-barhocker-anthrazit-60400745/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -776,23 +804,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUNDE Klapphocker</t>
+          <t>YNGVAR Barhocker</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9069</v>
+        <v>0.9227</v>
       </c>
       <c r="E11" t="n">
         <v>4.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>12.99</v>
+        <v>179</v>
       </c>
       <c r="H11" t="n">
-        <v>5.99</v>
+        <v>23.96</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -800,88 +828,40 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18.98</v>
+        <v>1813.96</v>
       </c>
       <c r="K11" t="n">
-        <v>18.98</v>
+        <v>181.4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/gunde-klapphocker-schwarz-40570404/</t>
+          <t>https://www.ikea.com/de/de/p/yngvar-barhocker-anthrazit-60400745/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IKEA Deutschland</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GUNDE Klapphocker</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9069</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12.99</v>
-      </c>
+          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>23.96</v>
+        <v>27</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>parcel estimate (3/package)</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>153.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://www.ikea.com/de/de/p/gunde-klapphocker-schwarz-40570404/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>↳ pickup alternative: IKEA Ludwigsburg</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>27</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>90 km round trip @ 0.30 €/km, one trip/order</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -968,19 +948,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>home deluxe hocker stapelhocker nivo 10 st esszimmerhocker fusshocker rund S0BFF0NA</t>
+          <t>YNGVAR Barhocker</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9112</v>
+        <v>0.9227</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -989,7 +969,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/home-deluxe-hocker-stapelhocker-nivo-10-st-esszimmerhocker-fusshocker-rund-S0BFF0NA/</t>
+          <t>https://www.ikea.com/de/de/p/yngvar-barhocker-anthrazit-60400745/</t>
         </is>
       </c>
     </row>
@@ -1001,14 +981,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GUNDE Klapphocker</t>
+          <t>FRANKLIN Barhocker, zusammenklappbar</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9069</v>
+        <v>0.9164</v>
       </c>
       <c r="D4" t="n">
-        <v>12.99</v>
+        <v>44.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1017,26 +997,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/gunde-klapphocker-schwarz-40570404/</t>
+          <t>https://www.ikea.com/de/de/p/franklin-barhocker-zusammenklappbar-arbeitsplattenhoehe-schwarz-schwarz-50406465/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>clp barhocker joshua metall 1er stapelbarer barstuhl aus metall mit fussablagen S0K030T3</t>
+          <t>ROSENTORP Barhocker</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8885</v>
+        <v>0.9039</v>
       </c>
       <c r="D5" t="n">
-        <v>57.9</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1045,26 +1025,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/clp-barhocker-joshua-metall-1er-stapelbarer-barstuhl-aus-metall-mit-fussablagen-S0K030T3/</t>
+          <t>https://www.ikea.com/de/de/p/rosentorp-barhocker-arbeitsplattenhoehe-weiss-50618194/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DALFRED Barhocker</t>
+          <t>clp barhocker peony aus pulverbeschichtetem metall minimalistischer look S07F90A9</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8875</v>
+        <v>0.901</v>
       </c>
       <c r="D6" t="n">
-        <v>49.99</v>
+        <v>32.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1073,7 +1053,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/dalfred-barhocker-schwarz-60155602/</t>
+          <t>https://www.otto.de/p/clp-barhocker-peony-aus-pulverbeschichtetem-metall-minimalistischer-look-S07F90A9/</t>
         </is>
       </c>
     </row>
@@ -1085,14 +1065,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GUNDE / GUNDE Tisch + 2 Hocker</t>
+          <t>SYNTORP Barhocker</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8831</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="n">
-        <v>60.97</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1101,7 +1081,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/gunde-gunde-tisch-2-hocker-klappbar-schwarz-klappbar-schwarz-s19564749/</t>
+          <t>https://www.ikea.com/de/de/p/syntorp-barhocker-arbeitsplattenhoehe-schwarz-knaebaeck-anthrazit-90615004/</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1093,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KULLABERG Hocker</t>
+          <t>SKOGSTA Barhocker</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8796</v>
+        <v>0.8929</v>
       </c>
       <c r="D8" t="n">
-        <v>59.99</v>
+        <v>69</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1129,26 +1109,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/kullaberg-hocker-kiefer-schwarz-10363651/</t>
+          <t>https://www.ikea.com/de/de/p/skogsta-barhocker-arbeitsplattenhoehe-schwarz-00621009/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RUDSTORP Hocker</t>
+          <t>clp barhocker joshua metall 1er stapelbarer barstuhl aus metall mit fussablagen S0K030T3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8791</v>
+        <v>0.8885</v>
       </c>
       <c r="D9" t="n">
-        <v>29.99</v>
+        <v>57.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1157,26 +1137,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/rudstorp-hocker-schwarz-60610102/</t>
+          <t>https://www.otto.de/p/clp-barhocker-joshua-metall-1er-stapelbarer-barstuhl-aus-metall-mit-fussablagen-S0K030T3/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>stuhlmann sitzhocker roma p1004 1 st schminktischhocker sitzhocker aus kunstleder mit holz</t>
+          <t>DALFRED Barhocker</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8777</v>
+        <v>0.8875</v>
       </c>
       <c r="D10" t="n">
-        <v>29.99</v>
+        <v>49.99</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1185,7 +1165,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/stuhlmann-sitzhocker-roma-p1004-1-st-schminktischhocker-sitzhocker-aus-kunstleder-mit-holzbeinen-runder-hocker-S0PCS0KH/</t>
+          <t>https://www.ikea.com/de/de/p/dalfred-barhocker-schwarz-60155602/</t>
         </is>
       </c>
     </row>
@@ -1197,14 +1177,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOMSTEN Hocker</t>
+          <t>NORDVIKEN Barhocker</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8633</v>
+        <v>0.8837</v>
       </c>
       <c r="D11" t="n">
-        <v>29.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1213,54 +1193,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/domsten-hocker-orange-kiefer-30555159/</t>
+          <t>https://www.ikea.com/de/de/p/nordviken-barhocker-arbeitsplattenhoehe-antikbeize-10488547/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>haku beistelltisch sofatisch wohnzimmertisch 1 st quadratisch aus metall anthrazit b t h 3</t>
+          <t>JANINGE Barhocker</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8619</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>79.98999999999999</v>
+        <v>139</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/haku-beistelltisch-sofatisch-wohnzimmertisch-1-st-quadratisch-aus-metall-anthrazit-b-t-h-39-39-55-cm-2095861850/</t>
+          <t>https://www.ikea.com/de/de/p/janinge-barhocker-grau-10281354/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>homsee hocker rollhocker mit schublade schwarz mdf metall 40 40 35 cm 1 st S03G60QJ</t>
+          <t>BERGMUND Barhocker</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.8596</v>
+        <v>0.8811</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1269,26 +1249,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/homsee-hocker-rollhocker-mit-schublade-schwarz-mdf-metall-40-40-35-cm-1-st-S03G60QJ/</t>
+          <t>https://www.ikea.com/de/de/p/bergmund-barhocker-arbeitsplattenhoehe-schwarz-glose-schwarz-80451989/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARIUS Hocker</t>
+          <t>clp barhocker joshua metall set 4er stapelbare barstuehle aus metall mit fussablagen S0K03</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8516</v>
+        <v>0.8778</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>174.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1297,26 +1277,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/marius-hocker-schwarz-10135659/</t>
+          <t>https://www.otto.de/p/clp-barhocker-joshua-metall-set-4er-stapelbare-barstuehle-aus-metall-mit-fussablagen-S0K030VI/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>baario sitzhocker hocker selce industrial style hoehenverstellbar eisen schwarz vintage S0</t>
+          <t>RÄVSTEN Barhocker</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8507</v>
+        <v>0.8757</v>
       </c>
       <c r="D15" t="n">
-        <v>149</v>
+        <v>59.99</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1325,26 +1305,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/baario-sitzhocker-hocker-selce-industrial-style-hoehenverstellbar-eisen-schwarz-vintage-S0Z2A0HE/</t>
+          <t>https://www.ikea.com/de/de/p/raevsten-barhocker-arbeitsplattenhoehe-schwarz-70602069/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BLYKOBB Hocker mit Rollen</t>
+          <t>clp barhocker mapun 1er hoehenverstellbar bodenschoner S0OGY0NK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8435</v>
+        <v>0.8703</v>
       </c>
       <c r="D16" t="n">
-        <v>99.98999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1353,35 +1333,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/blykobb-hocker-mit-rollen-glose-schwarz-00489378/</t>
+          <t>https://www.otto.de/p/clp-barhocker-mapun-1er-hoehenverstellbar-bodenschoner-S0OGY0NK/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>IKEA Deutschland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clp sitzbank barci mit schwarzem metallgestell sitzflaeche gepolstert S06E00VD</t>
+          <t>BERGMUND Barhocker</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8356</v>
+        <v>0.8643</v>
       </c>
       <c r="D17" t="n">
-        <v>74.90000000000001</v>
+        <v>102.99</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/clp-sitzbank-barci-mit-schwarzem-metallgestell-sitzflaeche-gepolstert-S06E00VD/</t>
+          <t>https://www.ikea.com/de/de/p/bergmund-barhocker-arbeitsplattenhoehe-eichenachbildung-gunnared-mittelgrau-s19384705/</t>
         </is>
       </c>
     </row>
@@ -1393,23 +1373,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eugad beistelltisch 1 st rund balkontisch gartentisch aus metall 48xh45cm S0VB506S</t>
+          <t>woltu barhocker 2 st barstuhl aus hochwertigem kunstleder verchromter stahl S060K04V</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8215</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>20.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/eugad-beistelltisch-1-st-rund-balkontisch-gartentisch-aus-metall-48xh45cm-S0VB506S/</t>
+          <t>https://www.otto.de/p/woltu-barhocker-2-st-barstuhl-aus-hochwertigem-kunstleder-verchromter-stahl-S060K04V/</t>
         </is>
       </c>
     </row>
@@ -1421,42 +1401,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>woltu beistelltisch 1 st mit stauraum 2 abnehmbare tabletts rund aus metall S0GAG03V</t>
+          <t>lovinghome barhocker barstuhl barhocker durable m1 edelstahl gebuerstet schwarz 1 stueck m</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8187</v>
+        <v>0.8466</v>
       </c>
       <c r="D19" t="n">
-        <v>22.09</v>
+        <v>169</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.otto.de/p/woltu-beistelltisch-1-st-mit-stauraum-2-abnehmbare-tabletts-rund-aus-metall-S0GAG03V/</t>
+          <t>https://www.otto.de/p/lovinghome-barhocker-barstuhl-barhocker-durable-m1-edelstahl-gebuerstet-schwarz-1-stueck-mit-fussablage-hoehenverstellbar-fester-stand-dank-grosser-base-S0A9N06W/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IKEA Deutschland</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LANDSKRONA Hocker</t>
+          <t>eugad barhocker 2 st aus kunstleder und stahl stufenlos hoehenverstellbar S021Q0H9</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8169</v>
+        <v>0.8454</v>
       </c>
       <c r="D20" t="n">
-        <v>299</v>
+        <v>116.96</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1465,35 +1445,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ikea.com/de/de/p/landskrona-hocker-grann-bomstad-schwarz-metall-s89031809/</t>
+          <t>https://www.otto.de/p/eugad-barhocker-2-st-aus-kunstleder-und-stahl-stufenlos-hoehenverstellbar-S021Q0H9/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POCO Einrichtungsmärkte</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kommode kerry 01b eiche artisan nachbildung kaschmir b h t ca 60x85x35 cm 511355300</t>
+          <t>actona group barhocker in schwarz polyurethan stahl 47x110x51cm bxhxt CS0FBK0EE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.7708</v>
+        <v>0.836</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>149.95</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>clip-zero-shot</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.poco.de/p/kommode-kerry-01b-eiche-artisan-nachbildung-kaschmir-b-h-t-ca-60x85x35-cm-511355300</t>
+          <t>https://www.otto.de/p/actona-group-barhocker-in-schwarz-polyurethan-stahl-47x110x51cm-bxhxt-CS0FBK0EE/</t>
         </is>
       </c>
     </row>
